--- a/results/metrics/model_results.xlsx
+++ b/results/metrics/model_results.xlsx
@@ -1,45 +1,106 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emade\Downloads\Dementia_Detection\results\metrics\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B9DE80-5414-4A3E-A753-029B5A85AE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="1020" yWindow="2800" windowWidth="13080" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Results" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+  <si>
+    <t>Model</t>
+  </si>
+  <si>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>F1 (weighted)</t>
+  </si>
+  <si>
+    <t>AUC-ROC (OvR)</t>
+  </si>
+  <si>
+    <t>CV Acc (mean)</t>
+  </si>
+  <si>
+    <t>CV Acc (std)</t>
+  </si>
+  <si>
+    <t>Train Time (s)</t>
+  </si>
+  <si>
+    <t>Logistic Regression</t>
+  </si>
+  <si>
+    <t>Decision Tree</t>
+  </si>
+  <si>
+    <t>Random Forest</t>
+  </si>
+  <si>
+    <t>Gradient Boosting</t>
+  </si>
+  <si>
+    <t>XGBoost</t>
+  </si>
+  <si>
+    <t>SVM</t>
+  </si>
+  <si>
+    <t>KNN</t>
+  </si>
+  <si>
+    <t>Naive Bayes</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001565C0"/>
+        <fgColor rgb="FF1565C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -56,83 +117,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,249 +422,224 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G9"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Model</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Accuracy</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>F1 (weighted)</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>AUC-ROC (OvR)</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>CV Acc (mean)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CV Acc (std)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Train Time (s)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Logistic Regression</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>0.9322</v>
-      </c>
-      <c r="C2" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.979</v>
-      </c>
-      <c r="E2" t="n">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>0.93220000000000003</v>
+      </c>
+      <c r="C2">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="D2">
+        <v>0.97899999999999998</v>
+      </c>
+      <c r="E2">
         <v>0.8992</v>
       </c>
-      <c r="F2" t="n">
-        <v>0.023</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.117</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Decision Tree</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>0.8643999999999999</v>
-      </c>
-      <c r="C3" t="n">
-        <v>0.8643999999999999</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="F2">
+        <v>2.3E-2</v>
+      </c>
+      <c r="G2">
+        <v>0.11700000000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3">
+        <v>0.86439999999999995</v>
+      </c>
+      <c r="C3">
+        <v>0.86439999999999995</v>
+      </c>
+      <c r="D3">
         <v>0.8911</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.8797</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0314</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.039</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Random Forest</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0.8983</v>
-      </c>
-      <c r="C4" t="n">
-        <v>0.8707</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.9346</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9147</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.0155</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="E3">
+        <v>0.87970000000000004</v>
+      </c>
+      <c r="F3">
+        <v>3.1399999999999997E-2</v>
+      </c>
+      <c r="G3">
+        <v>3.9E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4">
+        <v>0.89829999999999999</v>
+      </c>
+      <c r="C4">
+        <v>0.87070000000000003</v>
+      </c>
+      <c r="D4">
+        <v>0.93459999999999999</v>
+      </c>
+      <c r="E4">
+        <v>0.91469999999999996</v>
+      </c>
+      <c r="F4">
+        <v>1.55E-2</v>
+      </c>
+      <c r="G4">
         <v>1.732</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Gradient Boosting</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>0.8814</v>
-      </c>
-      <c r="C5" t="n">
-        <v>0.8344</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.9135</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9069</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.0148</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3.716</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>XGBoost</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>0.8643999999999999</v>
-      </c>
-      <c r="C6" t="n">
-        <v>0.8258</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.9532</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9109</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.0194</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2.803</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5">
+        <v>0.88139999999999996</v>
+      </c>
+      <c r="C5">
+        <v>0.83440000000000003</v>
+      </c>
+      <c r="D5">
+        <v>0.91349999999999998</v>
+      </c>
+      <c r="E5">
+        <v>0.90690000000000004</v>
+      </c>
+      <c r="F5">
+        <v>1.4800000000000001E-2</v>
+      </c>
+      <c r="G5">
+        <v>3.7160000000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>0.86439999999999995</v>
+      </c>
+      <c r="C6">
+        <v>0.82579999999999998</v>
+      </c>
+      <c r="D6">
+        <v>0.95320000000000005</v>
+      </c>
+      <c r="E6">
+        <v>0.91090000000000004</v>
+      </c>
+      <c r="F6">
+        <v>1.9400000000000001E-2</v>
+      </c>
+      <c r="G6">
+        <v>2.8029999999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7">
         <v>0.9153</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.9001</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.9515</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8955</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.0191</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="C7">
+        <v>0.90010000000000001</v>
+      </c>
+      <c r="D7">
+        <v>0.95150000000000001</v>
+      </c>
+      <c r="E7">
+        <v>0.89549999999999996</v>
+      </c>
+      <c r="F7">
+        <v>1.9099999999999999E-2</v>
+      </c>
+      <c r="G7">
         <v>0.152</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>KNN</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.8305</v>
-      </c>
-      <c r="C8" t="n">
-        <v>0.788</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.8605</v>
-      </c>
-      <c r="E8" t="n">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8">
+        <v>0.83050000000000002</v>
+      </c>
+      <c r="C8">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="D8">
+        <v>0.86050000000000004</v>
+      </c>
+      <c r="E8">
         <v>0.8488</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.0532</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.042</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Naive Bayes</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.9322</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.925</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="F8">
+        <v>5.3199999999999997E-2</v>
+      </c>
+      <c r="G8">
+        <v>4.2000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9">
+        <v>0.93220000000000003</v>
+      </c>
+      <c r="C9">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="D9">
         <v>0.9325</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.8915</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.0196</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.023</v>
+      <c r="E9">
+        <v>0.89149999999999996</v>
+      </c>
+      <c r="F9">
+        <v>1.9599999999999999E-2</v>
+      </c>
+      <c r="G9">
+        <v>2.3E-2</v>
       </c>
     </row>
   </sheetData>

--- a/results/metrics/model_results.xlsx
+++ b/results/metrics/model_results.xlsx
@@ -1,106 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emade\Downloads\Dementia_Detection\results\metrics\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B9DE80-5414-4A3E-A753-029B5A85AE9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="1020" yWindow="2800" windowWidth="13080" windowHeight="9970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Model Results" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
-  <si>
-    <t>Model</t>
-  </si>
-  <si>
-    <t>Accuracy</t>
-  </si>
-  <si>
-    <t>F1 (weighted)</t>
-  </si>
-  <si>
-    <t>AUC-ROC (OvR)</t>
-  </si>
-  <si>
-    <t>CV Acc (mean)</t>
-  </si>
-  <si>
-    <t>CV Acc (std)</t>
-  </si>
-  <si>
-    <t>Train Time (s)</t>
-  </si>
-  <si>
-    <t>Logistic Regression</t>
-  </si>
-  <si>
-    <t>Decision Tree</t>
-  </si>
-  <si>
-    <t>Random Forest</t>
-  </si>
-  <si>
-    <t>Gradient Boosting</t>
-  </si>
-  <si>
-    <t>XGBoost</t>
-  </si>
-  <si>
-    <t>SVM</t>
-  </si>
-  <si>
-    <t>KNN</t>
-  </si>
-  <si>
-    <t>Naive Bayes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1565C0"/>
+        <fgColor rgb="001565C0"/>
       </patternFill>
     </fill>
   </fills>
@@ -117,24 +56,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -422,224 +420,258 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col width="23" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2">
-        <v>0.93220000000000003</v>
-      </c>
-      <c r="C2">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="D2">
-        <v>0.97899999999999998</v>
-      </c>
-      <c r="E2">
-        <v>0.8992</v>
-      </c>
-      <c r="F2">
-        <v>2.3E-2</v>
-      </c>
-      <c r="G2">
-        <v>0.11700000000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3">
-        <v>0.86439999999999995</v>
-      </c>
-      <c r="C3">
-        <v>0.86439999999999995</v>
-      </c>
-      <c r="D3">
-        <v>0.8911</v>
-      </c>
-      <c r="E3">
-        <v>0.87970000000000004</v>
-      </c>
-      <c r="F3">
-        <v>3.1399999999999997E-2</v>
-      </c>
-      <c r="G3">
-        <v>3.9E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4">
-        <v>0.89829999999999999</v>
-      </c>
-      <c r="C4">
-        <v>0.87070000000000003</v>
-      </c>
-      <c r="D4">
-        <v>0.93459999999999999</v>
-      </c>
-      <c r="E4">
-        <v>0.91469999999999996</v>
-      </c>
-      <c r="F4">
-        <v>1.55E-2</v>
-      </c>
-      <c r="G4">
-        <v>1.732</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5">
-        <v>0.88139999999999996</v>
-      </c>
-      <c r="C5">
-        <v>0.83440000000000003</v>
-      </c>
-      <c r="D5">
-        <v>0.91349999999999998</v>
-      </c>
-      <c r="E5">
-        <v>0.90690000000000004</v>
-      </c>
-      <c r="F5">
-        <v>1.4800000000000001E-2</v>
-      </c>
-      <c r="G5">
-        <v>3.7160000000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>11</v>
-      </c>
-      <c r="B6">
-        <v>0.86439999999999995</v>
-      </c>
-      <c r="C6">
-        <v>0.82579999999999998</v>
-      </c>
-      <c r="D6">
-        <v>0.95320000000000005</v>
-      </c>
-      <c r="E6">
-        <v>0.91090000000000004</v>
-      </c>
-      <c r="F6">
-        <v>1.9400000000000001E-2</v>
-      </c>
-      <c r="G6">
-        <v>2.8029999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>12</v>
-      </c>
-      <c r="B7">
-        <v>0.9153</v>
-      </c>
-      <c r="C7">
-        <v>0.90010000000000001</v>
-      </c>
-      <c r="D7">
-        <v>0.95150000000000001</v>
-      </c>
-      <c r="E7">
-        <v>0.89549999999999996</v>
-      </c>
-      <c r="F7">
-        <v>1.9099999999999999E-2</v>
-      </c>
-      <c r="G7">
-        <v>0.152</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8">
-        <v>0.83050000000000002</v>
-      </c>
-      <c r="C8">
-        <v>0.78800000000000003</v>
-      </c>
-      <c r="D8">
-        <v>0.86050000000000004</v>
-      </c>
-      <c r="E8">
-        <v>0.8488</v>
-      </c>
-      <c r="F8">
-        <v>5.3199999999999997E-2</v>
-      </c>
-      <c r="G8">
-        <v>4.2000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>14</v>
-      </c>
-      <c r="B9">
-        <v>0.93220000000000003</v>
-      </c>
-      <c r="C9">
-        <v>0.92500000000000004</v>
-      </c>
-      <c r="D9">
-        <v>0.9325</v>
-      </c>
-      <c r="E9">
-        <v>0.89149999999999996</v>
-      </c>
-      <c r="F9">
-        <v>1.9599999999999999E-2</v>
-      </c>
-      <c r="G9">
-        <v>2.3E-2</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Accuracy</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>F1 (weighted)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>AUC-ROC (OvR)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>CV Acc (mean)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>CV Acc (std)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Train Time (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Naive Bayes</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9322</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.9313</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8949</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.039</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>0.8814</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.9141</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.9078000000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0271</v>
+      </c>
+      <c r="G3" t="n">
+        <v>7.38</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>XGBoost</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>0.8814</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.9428</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3.626</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Random Forest</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.8814</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.8344</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.9109</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.0213</v>
+      </c>
+      <c r="G5" t="n">
+        <v>5.872</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SVM</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.8555</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.9491000000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.8756</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.148</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Decision Tree</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8475</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8535</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.9141</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.8218</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.0248</v>
+      </c>
+      <c r="G7" t="n">
+        <v>4.375</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>KNN</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.8305</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.788</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.8614000000000001</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.8821</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0312</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.044</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Logistic Regression</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.7966</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.8198</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.9713000000000001</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.8632</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.029</v>
+      </c>
+      <c r="G9" t="n">
+        <v>6.187</v>
       </c>
     </row>
   </sheetData>
